--- a/files/九龙-西南九龙-维港滙 II.xlsx
+++ b/files/九龙-西南九龙-维港滙 II.xlsx
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27382,7 +27382,7 @@
           <t>A | 781呎 (3房)
 $2,250万
 $28,809/呎
-(25年-05月)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
@@ -27398,7 +27398,7 @@
           <t>C | 459呎 (2房)
 $1,343万
 $29,252/呎
-(26年-04月)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
@@ -29649,7 +29649,7 @@
           <t>A | 797呎 (3房)
 $2,130万
 $26,725/呎
-(26年-04月)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
